--- a/public/excel/product-import-sample.xlsx
+++ b/public/excel/product-import-sample.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>name</t>
   </si>
@@ -52,12 +52,6 @@
     <t>video_url</t>
   </si>
   <si>
-    <t>is_catalog</t>
-  </si>
-  <si>
-    <t>external_link</t>
-  </si>
-  <si>
     <t>is_refundable</t>
   </si>
   <si>
@@ -82,7 +76,7 @@
     <t>pc</t>
   </si>
   <si>
-    <t>YR-104552742</t>
+    <t>PR-104552742</t>
   </si>
   <si>
     <t>DEM-012</t>
@@ -97,7 +91,7 @@
     <t>youtube</t>
   </si>
   <si>
-    <t>https://www.youtube.com/c/SpaGreenCreative</t>
+    <t>https://www.youtube.com/</t>
   </si>
   <si>
     <t>Demo Product short description</t>
@@ -116,7 +110,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -133,13 +127,8 @@
       <name val="Calibri"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF0563C1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -156,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -166,9 +155,6 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -444,10 +430,10 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="2" t="s">
@@ -462,16 +448,10 @@
       <c r="S1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>21</v>
+      <c r="A2" s="2" t="s">
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>1.0</v>
@@ -483,52 +463,49 @@
         <v>55.0</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="H2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="3">
+      <c r="J2" s="2">
         <v>100.0</v>
       </c>
       <c r="K2" s="2">
         <v>1.0</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="M2" s="5" t="s">
-        <v>28</v>
+        <v>25</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="N2" s="2">
         <v>0.0</v>
       </c>
-      <c r="P2" s="2">
+      <c r="O2" s="2">
         <v>0.0</v>
       </c>
-      <c r="Q2" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="R2" s="4" t="s">
+      <c r="P2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="S2" s="4" t="s">
+      <c r="S2" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
